--- a/data/trans_camb/IP24_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.611149456175953</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.5579473858224271</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.965091245675924</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.928058223112873</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.791946018207745</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.834743991851157</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-6.830434701718524</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.356293520916325</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.34669529915535</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.51766656769576</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-7.676204991883806</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-7.848238698024508</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.277315157252843</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.959139532095836</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3754795297389967</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.549133806932906</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3302598574670689</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.439584908884535</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.09951344053820214</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.0344618953813691</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.2298946892162798</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1128473995595067</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1810089818824332</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.08758171671886243</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.3513119326813331</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.4162324237159883</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.4182706384304113</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4164688138984725</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3291250856999627</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3438414715416949</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.2407308510028934</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.6033049192616091</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.01943310510001445</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3280265351568652</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01754701757161197</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2341746162706824</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.397979860831791</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5538656585573565</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7008056501633109</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.076646332628364</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.3531206317216817</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.3452890167688322</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-8.10834981353227</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.319850988488196</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.547154033753083</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.858689439576727</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.392969665876431</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-5.510607764364718</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>4.440911252761099</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.1553698754057</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.616852167212203</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.733149383616759</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.732902664639763</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.978935385076232</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.08006676248321509</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.03172165163018556</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.03189791912657301</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.04900470999070567</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01790576640107325</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01750864696003362</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3832730819465802</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.33019391018806</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.2213984001000772</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.3126115145057858</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2053004155406022</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2479991750003442</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.3053487361680274</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.9011089113882702</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3910780490307527</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3226247822160072</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2113729308114916</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.325893261104396</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>11.17881570897669</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.568826480118587</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11.43830431203119</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.899145349852214</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>11.35412114405977</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.711467879907224</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>4.744130422519667</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.588436223941176</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>4.287423195800569</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.447379002673627</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>6.384369832232172</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.5620222953450099</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>18.85961186895705</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.3978141011442</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>18.69292215993267</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.150318871129699</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>16.82063953010759</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.201729748714362</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.8942835721472367</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3654972558390402</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.7640331002077905</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1936513445678072</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.8276429103359971</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2705423025499486</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.2891973494676828</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.1146498579584511</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.2183601548409371</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1946217214269496</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.3645878375484322</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.03793421529198811</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>2.057009187171027</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.06023897022114</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.679259125608372</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.8018242669392953</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.390652617705982</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.7381274603593393</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.1521988096220783</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.4126735177641255</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>6.095181683256842</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.6360297266193637</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2.63765148309561</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.245687148106441</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-7.932312274878317</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-7.373328646272309</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.564044957226328</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.439719838173053</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.289940049942432</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-5.635726232312731</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>8.163507764441778</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>8.071406866616501</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>15.13591815429896</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6.173837945803743</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8.994098708971034</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>4.422616250224408</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.0101751346608066</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.02758897145533013</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.5413522003014704</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.05648988165658035</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1985218737775545</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.01849155330707739</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.4416408855630102</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3795070614582792</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.204335999250874</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.510387396838265</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.2111943079465244</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3505094892091239</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.8380774361781129</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.7912413110899906</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2.221414584708277</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.8497376898428104</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.9003246680851404</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.4502497561999651</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>1.238093111831012</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.180784853839742</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.315356940174184</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.723855337205663</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1.261037928455838</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.7478413044320287</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.989433981842935</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.406027024250566</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.153977409987667</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-6.193647793791229</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.015746749187023</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.293135510887078</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>4.173073587214558</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5.217847808169173</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>5.117293873910017</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.002971415498284</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>3.706099040060187</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.918435704904625</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.07931278770178542</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.07564159556269115</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.06394808573392671</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1324243855872121</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.06992664210165063</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.04146903916513037</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.115771774937791</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.1440822521874377</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.09633723850692212</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2790085025834398</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.05155459939835146</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.1707501122947711</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2910276111912808</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3657059107851727</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2769689239688826</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.05370281162234764</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2287882807469841</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1169132638919388</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
